--- a/data/Olahan Data Final.xlsx
+++ b/data/Olahan Data Final.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Skripsi\my\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FAE4936-3008-4AEA-9ADA-5DBCEDA9D5D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC5E3153-65B3-4A22-902F-DCCFA6C02493}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1830" yWindow="2670" windowWidth="21600" windowHeight="12645" firstSheet="5" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2020" sheetId="1" r:id="rId1"/>
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1716" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1764" uniqueCount="94">
   <si>
     <t>Provinsi</t>
   </si>
@@ -329,6 +329,27 @@
   </si>
   <si>
     <t>sum baru</t>
+  </si>
+  <si>
+    <t>Nama</t>
+  </si>
+  <si>
+    <t>Tahun</t>
+  </si>
+  <si>
+    <t>PC1 (Unweighted)</t>
+  </si>
+  <si>
+    <t>PC2 (Unweighted)</t>
+  </si>
+  <si>
+    <t>PC1 (STATIS)</t>
+  </si>
+  <si>
+    <t>PC2 (STATIS)</t>
+  </si>
+  <si>
+    <t>Jarak Euclidean</t>
   </si>
 </sst>
 </file>
@@ -12128,9 +12149,1000 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F663893-4EE9-457B-B4BB-9841DBFE082F}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:N42"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D1" t="s">
+        <v>90</v>
+      </c>
+      <c r="E1" t="s">
+        <v>91</v>
+      </c>
+      <c r="F1" t="s">
+        <v>92</v>
+      </c>
+      <c r="G1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2">
+        <v>2020</v>
+      </c>
+      <c r="C2">
+        <v>-1.25</v>
+      </c>
+      <c r="D2">
+        <v>1.3658999999999999</v>
+      </c>
+      <c r="E2">
+        <v>-2.4521999999999999</v>
+      </c>
+      <c r="F2">
+        <v>-1.6111</v>
+      </c>
+      <c r="G2">
+        <v>3.2105000000000001</v>
+      </c>
+      <c r="I2">
+        <f>E2-C2</f>
+        <v>-1.2021999999999999</v>
+      </c>
+      <c r="J2">
+        <f>F2-D2</f>
+        <v>-2.9769999999999999</v>
+      </c>
+      <c r="K2">
+        <f>I2^2</f>
+        <v>1.4452848399999998</v>
+      </c>
+      <c r="L2">
+        <f>J2^2</f>
+        <v>8.8625289999999985</v>
+      </c>
+      <c r="M2">
+        <f>K2+L2</f>
+        <v>10.307813839999998</v>
+      </c>
+      <c r="N2">
+        <f>SQRT(M2)</f>
+        <v>3.2105784276357427</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3">
+        <v>2020</v>
+      </c>
+      <c r="C3">
+        <v>5.0349000000000004</v>
+      </c>
+      <c r="D3">
+        <v>2.7699999999999999E-2</v>
+      </c>
+      <c r="E3">
+        <v>4.7991000000000001</v>
+      </c>
+      <c r="F3">
+        <v>-0.7581</v>
+      </c>
+      <c r="G3">
+        <v>0.82040000000000002</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4">
+        <v>2020</v>
+      </c>
+      <c r="C4">
+        <v>3.3633000000000002</v>
+      </c>
+      <c r="D4">
+        <v>-0.10970000000000001</v>
+      </c>
+      <c r="E4">
+        <v>3.3338000000000001</v>
+      </c>
+      <c r="F4">
+        <v>-0.85240000000000005</v>
+      </c>
+      <c r="G4">
+        <v>0.74329999999999996</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5">
+        <v>2020</v>
+      </c>
+      <c r="C5">
+        <v>4.218</v>
+      </c>
+      <c r="D5">
+        <v>6.3E-3</v>
+      </c>
+      <c r="E5">
+        <v>3.9373</v>
+      </c>
+      <c r="F5">
+        <v>-0.7</v>
+      </c>
+      <c r="G5">
+        <v>0.76</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6">
+        <v>2020</v>
+      </c>
+      <c r="C6">
+        <v>3.2227000000000001</v>
+      </c>
+      <c r="D6">
+        <v>0.2772</v>
+      </c>
+      <c r="E6">
+        <v>2.8784999999999998</v>
+      </c>
+      <c r="F6">
+        <v>-2.6700000000000002E-2</v>
+      </c>
+      <c r="G6">
+        <v>0.45910000000000001</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7">
+        <v>2020</v>
+      </c>
+      <c r="C7">
+        <v>2.9538000000000002</v>
+      </c>
+      <c r="D7">
+        <v>-0.3589</v>
+      </c>
+      <c r="E7">
+        <v>2.4767999999999999</v>
+      </c>
+      <c r="F7">
+        <v>-0.27650000000000002</v>
+      </c>
+      <c r="G7">
+        <v>0.48399999999999999</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8">
+        <v>2020</v>
+      </c>
+      <c r="C8">
+        <v>6.6799999999999998E-2</v>
+      </c>
+      <c r="D8">
+        <v>0.1517</v>
+      </c>
+      <c r="E8">
+        <v>-0.72709999999999997</v>
+      </c>
+      <c r="F8">
+        <v>1.7458</v>
+      </c>
+      <c r="G8">
+        <v>1.7808999999999999</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9">
+        <v>2020</v>
+      </c>
+      <c r="C9">
+        <v>-1.7807999999999999</v>
+      </c>
+      <c r="D9">
+        <v>-0.1487</v>
+      </c>
+      <c r="E9">
+        <v>-2.3195000000000001</v>
+      </c>
+      <c r="F9">
+        <v>0.25650000000000001</v>
+      </c>
+      <c r="G9">
+        <v>0.67400000000000004</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10">
+        <v>2020</v>
+      </c>
+      <c r="C10">
+        <v>-2.4344000000000001</v>
+      </c>
+      <c r="D10">
+        <v>-0.49930000000000002</v>
+      </c>
+      <c r="E10">
+        <v>-3.4314</v>
+      </c>
+      <c r="F10">
+        <v>-0.10489999999999999</v>
+      </c>
+      <c r="G10">
+        <v>1.0721000000000001</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11">
+        <v>2020</v>
+      </c>
+      <c r="C11">
+        <v>0.48880000000000001</v>
+      </c>
+      <c r="D11">
+        <v>-1.8345</v>
+      </c>
+      <c r="E11">
+        <v>0.47720000000000001</v>
+      </c>
+      <c r="F11">
+        <v>-6.1499999999999999E-2</v>
+      </c>
+      <c r="G11">
+        <v>1.7730999999999999</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12">
+        <v>2020</v>
+      </c>
+      <c r="C12">
+        <v>-2.0225</v>
+      </c>
+      <c r="D12">
+        <v>-0.56259999999999999</v>
+      </c>
+      <c r="E12">
+        <v>-2.4497</v>
+      </c>
+      <c r="F12">
+        <v>0.43240000000000001</v>
+      </c>
+      <c r="G12">
+        <v>1.0828</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13">
+        <v>2020</v>
+      </c>
+      <c r="C13">
+        <v>-3.1787999999999998</v>
+      </c>
+      <c r="D13">
+        <v>-0.9274</v>
+      </c>
+      <c r="E13">
+        <v>-4.1936</v>
+      </c>
+      <c r="F13">
+        <v>-1.8597999999999999</v>
+      </c>
+      <c r="G13">
+        <v>1.3781000000000001</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14">
+        <v>2020</v>
+      </c>
+      <c r="C14">
+        <v>-2.1655000000000002</v>
+      </c>
+      <c r="D14">
+        <v>-1.6012999999999999</v>
+      </c>
+      <c r="E14">
+        <v>-2.6145999999999998</v>
+      </c>
+      <c r="F14">
+        <v>-2.6101000000000001</v>
+      </c>
+      <c r="G14">
+        <v>1.1043000000000001</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15">
+        <v>2020</v>
+      </c>
+      <c r="C15">
+        <v>-1.0287999999999999</v>
+      </c>
+      <c r="D15">
+        <v>-1.331</v>
+      </c>
+      <c r="E15">
+        <v>-1.1541999999999999</v>
+      </c>
+      <c r="F15">
+        <v>1.2215</v>
+      </c>
+      <c r="G15">
+        <v>2.5556000000000001</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16">
+        <v>2020</v>
+      </c>
+      <c r="C16">
+        <v>-2.1433</v>
+      </c>
+      <c r="D16">
+        <v>-1.0755999999999999</v>
+      </c>
+      <c r="E16">
+        <v>-2.6482000000000001</v>
+      </c>
+      <c r="F16">
+        <v>1.0891</v>
+      </c>
+      <c r="G16">
+        <v>2.2227999999999999</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17">
+        <v>2020</v>
+      </c>
+      <c r="C17">
+        <v>-2.5589</v>
+      </c>
+      <c r="D17">
+        <v>-0.76659999999999995</v>
+      </c>
+      <c r="E17">
+        <v>-3.3801000000000001</v>
+      </c>
+      <c r="F17">
+        <v>-2.4937</v>
+      </c>
+      <c r="G17">
+        <v>1.9124000000000001</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>32</v>
+      </c>
+      <c r="B18">
+        <v>2020</v>
+      </c>
+      <c r="C18">
+        <v>-0.45860000000000001</v>
+      </c>
+      <c r="D18">
+        <v>-1.4258999999999999</v>
+      </c>
+      <c r="E18">
+        <v>-0.9607</v>
+      </c>
+      <c r="F18">
+        <v>-0.82440000000000002</v>
+      </c>
+      <c r="G18">
+        <v>0.78349999999999997</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>33</v>
+      </c>
+      <c r="B19">
+        <v>2020</v>
+      </c>
+      <c r="C19">
+        <v>-2.1255000000000002</v>
+      </c>
+      <c r="D19">
+        <v>-0.94579999999999997</v>
+      </c>
+      <c r="E19">
+        <v>-2.7970000000000002</v>
+      </c>
+      <c r="F19">
+        <v>-1.1084000000000001</v>
+      </c>
+      <c r="G19">
+        <v>0.69089999999999996</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>34</v>
+      </c>
+      <c r="B20">
+        <v>2020</v>
+      </c>
+      <c r="C20">
+        <v>-1.4645999999999999</v>
+      </c>
+      <c r="D20">
+        <v>-1.2931999999999999</v>
+      </c>
+      <c r="E20">
+        <v>-1.8541000000000001</v>
+      </c>
+      <c r="F20">
+        <v>-0.44090000000000001</v>
+      </c>
+      <c r="G20">
+        <v>0.93710000000000004</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>35</v>
+      </c>
+      <c r="B21">
+        <v>2020</v>
+      </c>
+      <c r="C21">
+        <v>-0.61650000000000005</v>
+      </c>
+      <c r="D21">
+        <v>-0.39219999999999999</v>
+      </c>
+      <c r="E21">
+        <v>-1.2034</v>
+      </c>
+      <c r="F21">
+        <v>1.1749000000000001</v>
+      </c>
+      <c r="G21">
+        <v>1.6733</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>36</v>
+      </c>
+      <c r="B22">
+        <v>2020</v>
+      </c>
+      <c r="C22">
+        <v>-0.26419999999999999</v>
+      </c>
+      <c r="D22">
+        <v>-8.4400000000000003E-2</v>
+      </c>
+      <c r="E22">
+        <v>-0.8155</v>
+      </c>
+      <c r="F22">
+        <v>0.16109999999999999</v>
+      </c>
+      <c r="G22">
+        <v>0.60340000000000005</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>37</v>
+      </c>
+      <c r="B23">
+        <v>2020</v>
+      </c>
+      <c r="C23">
+        <v>1.7746999999999999</v>
+      </c>
+      <c r="D23">
+        <v>-0.13550000000000001</v>
+      </c>
+      <c r="E23">
+        <v>1.5865</v>
+      </c>
+      <c r="F23">
+        <v>0.31609999999999999</v>
+      </c>
+      <c r="G23">
+        <v>0.48930000000000001</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>38</v>
+      </c>
+      <c r="B24">
+        <v>2020</v>
+      </c>
+      <c r="C24">
+        <v>-1.5406</v>
+      </c>
+      <c r="D24">
+        <v>-1.0946</v>
+      </c>
+      <c r="E24">
+        <v>-1.8895</v>
+      </c>
+      <c r="F24">
+        <v>2.2865000000000002</v>
+      </c>
+      <c r="G24">
+        <v>3.399</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>39</v>
+      </c>
+      <c r="B25">
+        <v>2020</v>
+      </c>
+      <c r="C25">
+        <v>-2.2536999999999998</v>
+      </c>
+      <c r="D25">
+        <v>-1.63</v>
+      </c>
+      <c r="E25">
+        <v>-2.9211999999999998</v>
+      </c>
+      <c r="F25">
+        <v>-3.8140999999999998</v>
+      </c>
+      <c r="G25">
+        <v>2.2837999999999998</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>40</v>
+      </c>
+      <c r="B26">
+        <v>2020</v>
+      </c>
+      <c r="C26">
+        <v>1.9126000000000001</v>
+      </c>
+      <c r="D26">
+        <v>-0.45889999999999997</v>
+      </c>
+      <c r="E26">
+        <v>1.7501</v>
+      </c>
+      <c r="F26">
+        <v>1.4993000000000001</v>
+      </c>
+      <c r="G26">
+        <v>1.9650000000000001</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>41</v>
+      </c>
+      <c r="B27">
+        <v>2020</v>
+      </c>
+      <c r="C27">
+        <v>1.1629</v>
+      </c>
+      <c r="D27">
+        <v>7.7899999999999997E-2</v>
+      </c>
+      <c r="E27">
+        <v>0.87180000000000002</v>
+      </c>
+      <c r="F27">
+        <v>1.9206000000000001</v>
+      </c>
+      <c r="G27">
+        <v>1.8655999999999999</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>42</v>
+      </c>
+      <c r="B28">
+        <v>2020</v>
+      </c>
+      <c r="C28">
+        <v>2.7121</v>
+      </c>
+      <c r="D28">
+        <v>-0.69920000000000004</v>
+      </c>
+      <c r="E28">
+        <v>2.6168999999999998</v>
+      </c>
+      <c r="F28">
+        <v>-2.8E-3</v>
+      </c>
+      <c r="G28">
+        <v>0.70289999999999997</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>43</v>
+      </c>
+      <c r="B29">
+        <v>2020</v>
+      </c>
+      <c r="C29">
+        <v>0.59350000000000003</v>
+      </c>
+      <c r="D29">
+        <v>-1.1888000000000001</v>
+      </c>
+      <c r="E29">
+        <v>9.5200000000000007E-2</v>
+      </c>
+      <c r="F29">
+        <v>0.37280000000000002</v>
+      </c>
+      <c r="G29">
+        <v>1.6392</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>44</v>
+      </c>
+      <c r="B30">
+        <v>2020</v>
+      </c>
+      <c r="C30">
+        <v>2.8776999999999999</v>
+      </c>
+      <c r="D30">
+        <v>-2.9100000000000001E-2</v>
+      </c>
+      <c r="E30">
+        <v>2.9563999999999999</v>
+      </c>
+      <c r="F30">
+        <v>-0.3795</v>
+      </c>
+      <c r="G30">
+        <v>0.35909999999999997</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>45</v>
+      </c>
+      <c r="B31">
+        <v>2020</v>
+      </c>
+      <c r="C31">
+        <v>2.9554</v>
+      </c>
+      <c r="D31">
+        <v>0.41699999999999998</v>
+      </c>
+      <c r="E31">
+        <v>3.0143</v>
+      </c>
+      <c r="F31">
+        <v>-0.72330000000000005</v>
+      </c>
+      <c r="G31">
+        <v>1.1417999999999999</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
+        <v>46</v>
+      </c>
+      <c r="B32">
+        <v>2020</v>
+      </c>
+      <c r="C32">
+        <v>2.0682</v>
+      </c>
+      <c r="D32">
+        <v>-0.1938</v>
+      </c>
+      <c r="E32">
+        <v>1.9211</v>
+      </c>
+      <c r="F32">
+        <v>1.2916000000000001</v>
+      </c>
+      <c r="G32">
+        <v>1.4926999999999999</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
+        <v>47</v>
+      </c>
+      <c r="B33">
+        <v>2020</v>
+      </c>
+      <c r="C33">
+        <v>-0.76370000000000005</v>
+      </c>
+      <c r="D33">
+        <v>-1.3447</v>
+      </c>
+      <c r="E33">
+        <v>-1.2844</v>
+      </c>
+      <c r="F33">
+        <v>-1.2099</v>
+      </c>
+      <c r="G33">
+        <v>0.53790000000000004</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
+        <v>48</v>
+      </c>
+      <c r="B34">
+        <v>2020</v>
+      </c>
+      <c r="C34">
+        <v>-1.7618</v>
+      </c>
+      <c r="D34">
+        <v>-0.1618</v>
+      </c>
+      <c r="E34">
+        <v>-2.3424</v>
+      </c>
+      <c r="F34">
+        <v>-1.9388000000000001</v>
+      </c>
+      <c r="G34">
+        <v>1.8694999999999999</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
+        <v>50</v>
+      </c>
+      <c r="B35">
+        <v>2020</v>
+      </c>
+      <c r="C35">
+        <v>-3.4931000000000001</v>
+      </c>
+      <c r="D35">
+        <v>2.9477000000000002</v>
+      </c>
+      <c r="E35">
+        <v>-5.4337999999999997</v>
+      </c>
+      <c r="F35">
+        <v>-0.64439999999999997</v>
+      </c>
+      <c r="G35">
+        <v>4.0827999999999998</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
+        <v>51</v>
+      </c>
+      <c r="B36">
+        <v>2020</v>
+      </c>
+      <c r="C36">
+        <v>-3.7262</v>
+      </c>
+      <c r="D36">
+        <v>1.3238000000000001</v>
+      </c>
+      <c r="E36">
+        <v>-5.2637999999999998</v>
+      </c>
+      <c r="F36">
+        <v>-1.1177999999999999</v>
+      </c>
+      <c r="G36">
+        <v>2.8854000000000002</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
+        <v>52</v>
+      </c>
+      <c r="B37">
+        <v>2020</v>
+      </c>
+      <c r="C37">
+        <v>-0.1618</v>
+      </c>
+      <c r="D37">
+        <v>2.2189000000000001</v>
+      </c>
+      <c r="E37">
+        <v>-1.2805</v>
+      </c>
+      <c r="F37">
+        <v>-3.1800000000000002E-2</v>
+      </c>
+      <c r="G37">
+        <v>2.5133999999999999</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
+        <v>53</v>
+      </c>
+      <c r="B38">
+        <v>2020</v>
+      </c>
+      <c r="C38">
+        <v>-2.0754000000000001</v>
+      </c>
+      <c r="D38">
+        <v>3.9257</v>
+      </c>
+      <c r="E38">
+        <v>-4.1712999999999996</v>
+      </c>
+      <c r="F38">
+        <v>-0.43619999999999998</v>
+      </c>
+      <c r="G38">
+        <v>4.8392999999999997</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A39" t="s">
+        <v>54</v>
+      </c>
+      <c r="B39">
+        <v>2020</v>
+      </c>
+      <c r="C39">
+        <v>1.7627999999999999</v>
+      </c>
+      <c r="D39">
+        <v>1.1788000000000001</v>
+      </c>
+      <c r="E39">
+        <v>1.1477999999999999</v>
+      </c>
+      <c r="F39">
+        <v>-1.7141999999999999</v>
+      </c>
+      <c r="G39">
+        <v>2.9577</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A40" t="s">
+        <v>55</v>
+      </c>
+      <c r="B40">
+        <v>2020</v>
+      </c>
+      <c r="C40">
+        <v>3.2800000000000003E-2</v>
+      </c>
+      <c r="D40">
+        <v>3.1236999999999999</v>
+      </c>
+      <c r="E40">
+        <v>-1.6253</v>
+      </c>
+      <c r="F40">
+        <v>0.45989999999999998</v>
+      </c>
+      <c r="G40">
+        <v>3.1377000000000002</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A41" t="s">
+        <v>56</v>
+      </c>
+      <c r="B41">
+        <v>2020</v>
+      </c>
+      <c r="C41">
+        <v>-0.54090000000000005</v>
+      </c>
+      <c r="D41">
+        <v>2.3001999999999998</v>
+      </c>
+      <c r="E41">
+        <v>-1.8072999999999999</v>
+      </c>
+      <c r="F41">
+        <v>-1.1201000000000001</v>
+      </c>
+      <c r="G41">
+        <v>3.6473</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A42" t="s">
+        <v>57</v>
+      </c>
+      <c r="B42">
+        <v>2020</v>
+      </c>
+      <c r="C42">
+        <v>2.6086</v>
+      </c>
+      <c r="D42">
+        <v>0.95099999999999996</v>
+      </c>
+      <c r="E42">
+        <v>2.2934000000000001</v>
+      </c>
+      <c r="F42">
+        <v>-1.2038</v>
+      </c>
+      <c r="G42">
+        <v>2.1777000000000002</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
